--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-patient-contact-relationship-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
